--- a/output/stock_quant_scores/EQR_balance_df.xlsx
+++ b/output/stock_quant_scores/EQR_balance_df.xlsx
@@ -1393,10 +1393,14 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>8653788000</v>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="H6" t="n">
+        <v>-364819000</v>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1404,15 +1408,21 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>10954948000</v>
+      </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
+      <c r="S6" t="n">
+        <v>1827063000</v>
+      </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="n">
+        <v>9483056000</v>
+      </c>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="n">
@@ -1421,7 +1431,9 @@
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr"/>
+      <c r="AE6" t="n">
+        <v>725055000</v>
+      </c>
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="n">
@@ -1433,7 +1445,9 @@
       <c r="AL6" t="inlineStr"/>
       <c r="AM6" t="inlineStr"/>
       <c r="AN6" t="inlineStr"/>
-      <c r="AO6" t="inlineStr"/>
+      <c r="AO6" t="n">
+        <v>21169241000</v>
+      </c>
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr"/>
       <c r="AR6" t="inlineStr"/>
@@ -1452,10 +1466,14 @@
       <c r="BA6" t="n">
         <v>0</v>
       </c>
-      <c r="BB6" t="inlineStr"/>
+      <c r="BB6" t="n">
+        <v>360236000</v>
+      </c>
       <c r="BC6" t="inlineStr"/>
       <c r="BD6" t="inlineStr"/>
-      <c r="BE6" t="inlineStr"/>
+      <c r="BE6" t="n">
+        <v>123832000</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
